--- a/data/trans_dic/IP21-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,02</t>
+          <t>2,66; 9,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,49</t>
+          <t>0,63; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,88</t>
+          <t>0,43; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,33</t>
+          <t>1,94; 8,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,85</t>
+          <t>0,69; 6,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,94</t>
+          <t>0,55; 5,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,19</t>
+          <t>0,64; 4,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,69</t>
+          <t>2,74; 7,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,93</t>
+          <t>0,63; 3,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,26</t>
+          <t>0,91; 4,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,79</t>
+          <t>0,72; 3,9</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,6</t>
+          <t>2,83; 10,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,78</t>
+          <t>0,67; 5,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,6</t>
+          <t>1,07; 6,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,97</t>
+          <t>0,77; 6,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,16</t>
+          <t>0,97; 8,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,96</t>
+          <t>0,79; 7,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,72</t>
+          <t>1,49; 7,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,89</t>
+          <t>2,58; 7,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,18</t>
+          <t>1,07; 4,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,57</t>
+          <t>1,73; 5,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,13</t>
+          <t>0,61; 3,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,83</t>
+          <t>0,72; 5,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,62</t>
+          <t>0,87; 7,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,13</t>
+          <t>2,67; 9,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,06</t>
+          <t>2,24; 9,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 11,0</t>
+          <t>1,94; 11,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,47</t>
+          <t>1,65; 6,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,08</t>
+          <t>1,58; 6,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,37</t>
+          <t>1,92; 7,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,59</t>
+          <t>0,29; 3,54</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,15</t>
+          <t>1,92; 6,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,27</t>
+          <t>4,31; 10,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,16</t>
+          <t>0,73; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,2</t>
+          <t>0,2; 2,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,0</t>
+          <t>2,68; 7,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,98</t>
+          <t>2,79; 7,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,47</t>
+          <t>0,7; 4,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,18</t>
+          <t>0,84; 5,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,96</t>
+          <t>2,79; 6,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,04</t>
+          <t>4,19; 7,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,4</t>
+          <t>1,02; 3,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,02</t>
+          <t>0,73; 3,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,77</t>
+          <t>1,15; 7,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,46</t>
+          <t>1,36; 6,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,51</t>
+          <t>1,98; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,07</t>
+          <t>0,55; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,82</t>
+          <t>1,57; 7,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,12</t>
+          <t>2,24; 8,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,96</t>
+          <t>1,73; 8,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,65</t>
+          <t>0,59; 4,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,9</t>
+          <t>1,67; 5,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,32</t>
+          <t>2,41; 6,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,38</t>
+          <t>2,57; 6,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,74</t>
+          <t>0,83; 3,62</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,82; 7,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,76</t>
+          <t>0,91; 10,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 11,66</t>
+          <t>2,03; 11,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 11,83</t>
+          <t>2,62; 12,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,73</t>
+          <t>2,12; 7,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,47</t>
+          <t>2,52; 8,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,05</t>
+          <t>0,89; 5,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,05</t>
+          <t>2,67; 5,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,13</t>
+          <t>2,74; 5,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,94</t>
+          <t>1,97; 4,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,32</t>
+          <t>0,82; 2,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,13</t>
+          <t>3,45; 5,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,71</t>
+          <t>3,22; 5,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,18</t>
+          <t>1,92; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,74</t>
+          <t>0,98; 2,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,1</t>
+          <t>3,3; 5,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,05</t>
+          <t>3,32; 5,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,63</t>
+          <t>2,22; 3,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,2</t>
+          <t>1,08; 2,15</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3972</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9473</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2779; 10146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4218</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>522; 5593</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>449; 5768</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1888; 8051</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>611; 5336</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>552; 5011</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>873; 6424</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5542; 14963</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1134; 6866</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1665; 7841</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1743; 9409</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7189</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2475; 9589</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>626; 5310</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1131; 6512</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>729; 6607</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>838; 7200</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>757; 7158</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1678; 8474</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4481; 13842</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2032; 9199</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3784; 12228</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1161; 6994</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4034</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6083</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5749</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3356</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>622; 4942</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>535; 4674</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3060</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2655; 9876</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1935; 8094</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1463; 8761</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3033</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2743; 10977</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2720; 10774</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2632; 10416</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>340; 4093</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14545</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10898</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4790</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17138</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25443</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8669</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6499</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3861; 13036</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8881; 21664</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1620; 9032</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>432; 4946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5414; 15395</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6366; 17762</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1476; 8888</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1840; 11185</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11237; 24472</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18204; 33764</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4408; 14479</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3160; 13669</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4806</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5641</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5772</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2993</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11681</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>11412</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1202; 7455</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2021; 9676</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2699; 10294</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>652; 5979</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1994; 9517</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3139; 12215</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2475; 11497</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>956; 7499</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3868; 13814</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6973; 18268</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7176; 18745</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2346; 10202</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4076</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>6053</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6037</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>615; 5261</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4770</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>553; 6413</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1468; 8305</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1919; 8938</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4291</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3129; 11202</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3203; 10752</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1141; 7209</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4294</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>23559</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25900</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19211</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31195</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31290</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>54754</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>57190</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>39908</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>21675</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>17046; 32053</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18612; 34740</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13212; 26798</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5369; 14833</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23650; 40985</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>22971; 41733</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13614; 29222</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7319; 19337</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>43644; 66178</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>46171; 70532</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30610; 50910</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>15234; 30179</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,72</t>
+          <t>2,43; 9,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,73</t>
+          <t>0,64; 6,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,52</t>
+          <t>0,4; 4,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,25</t>
+          <t>1,98; 8,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,01</t>
+          <t>0,69; 6,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,02</t>
+          <t>0,55; 4,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,69</t>
+          <t>0,49; 4,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,41</t>
+          <t>2,64; 7,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,84</t>
+          <t>0,63; 3,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,29</t>
+          <t>0,78; 4,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,9</t>
+          <t>0,85; 3,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 10,97</t>
+          <t>2,85; 11,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,69</t>
+          <t>0,66; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,16</t>
+          <t>1,15; 6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,98</t>
+          <t>0,8; 6,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,38</t>
+          <t>0,86; 8,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,45</t>
+          <t>0,78; 7,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,52</t>
+          <t>1,38; 7,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,98</t>
+          <t>2,62; 7,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,86</t>
+          <t>1,08; 5,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,6</t>
+          <t>1,68; 5,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,68</t>
+          <t>0,58; 3,79</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,74</t>
+          <t>0,73; 7,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,56</t>
+          <t>0,86; 7,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,94</t>
+          <t>2,66; 10,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,38</t>
+          <t>2,22; 9,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,62</t>
+          <t>2,46; 12,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,58</t>
+          <t>1,64; 6,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,25</t>
+          <t>1,58; 6,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,59</t>
+          <t>2,05; 7,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,54</t>
+          <t>0,3; 3,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,49</t>
+          <t>1,89; 6,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,51</t>
+          <t>4,6; 10,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,06</t>
+          <t>0,76; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,27</t>
+          <t>0,2; 2,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,62</t>
+          <t>2,89; 7,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,79</t>
+          <t>2,81; 7,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,22</t>
+          <t>0,96; 4,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,12</t>
+          <t>0,89; 5,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,08</t>
+          <t>2,81; 6,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,78</t>
+          <t>4,19; 7,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,34</t>
+          <t>1,07; 3,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,14</t>
+          <t>0,67; 3,25</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,16</t>
+          <t>1,09; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,49</t>
+          <t>1,37; 6,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,56</t>
+          <t>1,91; 7,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,01</t>
+          <t>0,55; 5,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,48</t>
+          <t>1,54; 7,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,7</t>
+          <t>2,47; 9,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,03</t>
+          <t>1,69; 8,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,61</t>
+          <t>0,62; 4,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,97</t>
+          <t>1,82; 5,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,31</t>
+          <t>2,39; 6,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,71</t>
+          <t>2,28; 6,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,62</t>
+          <t>0,81; 3,48</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,03</t>
+          <t>0,81; 6,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,85</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,5</t>
+          <t>0,99; 9,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,47</t>
+          <t>2,55; 11,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 12,18</t>
+          <t>2,73; 12,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,61</t>
+          <t>2,04; 7,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,45</t>
+          <t>2,46; 8,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,59</t>
+          <t>0,89; 5,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,02</t>
+          <t>2,56; 4,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,12</t>
+          <t>2,8; 5,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,0</t>
+          <t>2,05; 3,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,26</t>
+          <t>0,79; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,99</t>
+          <t>3,45; 6,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,85</t>
+          <t>3,27; 5,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,12</t>
+          <t>1,99; 4,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,58</t>
+          <t>1,01; 2,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,0</t>
+          <t>3,34; 5,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,07</t>
+          <t>3,26; 5,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,69</t>
+          <t>2,21; 3,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,15</t>
+          <t>1,1; 2,24</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2779; 10146</t>
+          <t>2536; 9533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>522; 5593</t>
+          <t>529; 5137</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>449; 5768</t>
+          <t>422; 5177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1888; 8051</t>
+          <t>1935; 8659</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>611; 5336</t>
+          <t>615; 5647</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>552; 5011</t>
+          <t>545; 4677</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>873; 6424</t>
+          <t>676; 6435</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5542; 14963</t>
+          <t>5337; 14562</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1134; 6866</t>
+          <t>1119; 6945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1665; 7841</t>
+          <t>1426; 8041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1743; 9409</t>
+          <t>2047; 8749</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2475; 9589</t>
+          <t>2492; 9862</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>626; 5310</t>
+          <t>618; 5294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1131; 6512</t>
+          <t>1214; 7007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>729; 6607</t>
+          <t>756; 6444</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>838; 7200</t>
+          <t>737; 6975</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>757; 7158</t>
+          <t>746; 7032</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1678; 8474</t>
+          <t>1561; 8466</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4481; 13842</t>
+          <t>4544; 13783</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2032; 9199</t>
+          <t>2041; 9465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3784; 12228</t>
+          <t>3673; 12649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1161; 6994</t>
+          <t>1109; 7212</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3356</t>
+          <t>0; 2751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>622; 4942</t>
+          <t>625; 6074</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535; 4674</t>
+          <t>530; 4773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3060</t>
+          <t>0; 2883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2655; 9876</t>
+          <t>2646; 10259</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1935; 8094</t>
+          <t>1918; 8478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1463; 8761</t>
+          <t>1853; 9099</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3033</t>
+          <t>0; 3290</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2743; 10977</t>
+          <t>2735; 11358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2720; 10774</t>
+          <t>2733; 10567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2632; 10416</t>
+          <t>2809; 10546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>340; 4093</t>
+          <t>350; 4179</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3861; 13036</t>
+          <t>3798; 12221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8881; 21664</t>
+          <t>9472; 22411</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1620; 9032</t>
+          <t>1699; 9410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>432; 4946</t>
+          <t>435; 4595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5414; 15395</t>
+          <t>5832; 16037</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6366; 17762</t>
+          <t>6418; 17826</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1476; 8888</t>
+          <t>2028; 9524</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1840; 11185</t>
+          <t>1935; 11259</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11237; 24472</t>
+          <t>11319; 24585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18204; 33764</t>
+          <t>18194; 34280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4408; 14479</t>
+          <t>4651; 15325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3160; 13669</t>
+          <t>2922; 14170</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1202; 7455</t>
+          <t>1137; 7107</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2021; 9676</t>
+          <t>2040; 9037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2699; 10294</t>
+          <t>2601; 10287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>652; 5979</t>
+          <t>661; 6412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1994; 9517</t>
+          <t>1963; 10065</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3139; 12215</t>
+          <t>3463; 12744</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2475; 11497</t>
+          <t>2417; 11745</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>956; 7499</t>
+          <t>1012; 7431</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3868; 13814</t>
+          <t>4211; 12990</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6973; 18268</t>
+          <t>6914; 18965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7176; 18745</t>
+          <t>6357; 17628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2346; 10202</t>
+          <t>2275; 9822</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>615; 5261</t>
+          <t>607; 4883</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4770</t>
+          <t>0; 4231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>553; 6413</t>
+          <t>603; 6011</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1468; 8305</t>
+          <t>1846; 8488</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1919; 8938</t>
+          <t>2006; 9176</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4291</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3129; 11202</t>
+          <t>3005; 10943</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3203; 10752</t>
+          <t>3136; 11333</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1141; 7209</t>
+          <t>1145; 7396</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 4533</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17046; 32053</t>
+          <t>16350; 31758</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18612; 34740</t>
+          <t>19014; 35400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13212; 26798</t>
+          <t>13750; 26650</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5369; 14833</t>
+          <t>5158; 14938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23650; 40985</t>
+          <t>23618; 41305</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22971; 41733</t>
+          <t>23315; 41158</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13614; 29222</t>
+          <t>14103; 28715</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7319; 19337</t>
+          <t>7569; 19776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43644; 66178</t>
+          <t>44145; 66782</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46171; 70532</t>
+          <t>45405; 70448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30610; 50910</t>
+          <t>30498; 50318</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15234; 30179</t>
+          <t>15450; 31503</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,27%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,14</t>
+          <t>1,41; 8,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,69; 5,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,18</t>
+          <t>0,55; 4,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,96</t>
+          <t>0,38; 4,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,88</t>
+          <t>2,49; 10,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,36</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,69</t>
+          <t>0,65; 6,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,7</t>
+          <t>0,36; 5,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,21</t>
+          <t>2,78; 7,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,89</t>
+          <t>0,64; 3,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,4</t>
+          <t>0,7; 4,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,62</t>
+          <t>0,8; 3,69</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,29</t>
+          <t>0,92; 8,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,68</t>
+          <t>0,78; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,63</t>
+          <t>1,29; 7,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,81</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,11</t>
+          <t>2,85; 11,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,32</t>
+          <t>0,67; 5,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,51</t>
+          <t>1,13; 6,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,85; 6,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,95</t>
+          <t>2,43; 7,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,0</t>
+          <t>1,08; 5,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,79</t>
+          <t>1,72; 5,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,79</t>
+          <t>0,63; 4,11</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>2,65; 10,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,05</t>
+          <t>1,68; 10,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,72</t>
+          <t>1,77; 11,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,33</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,83</t>
+          <t>0,73; 6,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 12,06</t>
+          <t>0,88; 7,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,81</t>
+          <t>1,93; 6,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,13</t>
+          <t>1,58; 6,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,68</t>
+          <t>1,89; 7,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,61</t>
+          <t>0,23; 3,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,09</t>
+          <t>2,88; 8,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,87</t>
+          <t>2,91; 7,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,23</t>
+          <t>0,71; 4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,11</t>
+          <t>0,82; 5,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,94</t>
+          <t>1,89; 6,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,81</t>
+          <t>4,6; 10,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,52</t>
+          <t>0,85; 4,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,16</t>
+          <t>0,21; 2,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,1</t>
+          <t>2,91; 5,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,89</t>
+          <t>4,22; 8,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,54</t>
+          <t>1,07; 3,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,25</t>
+          <t>0,7; 3,47</t>
         </is>
       </c>
     </row>
@@ -1209,54 +1209,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,22%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,83</t>
+          <t>1,64; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,06</t>
+          <t>2,45; 9,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,55</t>
+          <t>1,77; 7,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,37</t>
+          <t>0,55; 4,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,91</t>
+          <t>1,14; 6,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,08</t>
+          <t>1,38; 6,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,21</t>
+          <t>2,19; 7,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,57</t>
+          <t>0,53; 4,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,61</t>
+          <t>1,74; 5,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,55</t>
+          <t>2,39; 6,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,31</t>
+          <t>2,33; 6,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,48</t>
+          <t>0,85; 3,55</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4,11%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,52</t>
+          <t>1,87; 11,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>2,66; 11,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,84</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,91</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,02</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 8,05</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1,73; 10,76</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2,55; 11,72</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 12,5</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,77</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,43</t>
+          <t>2,08; 7,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,9</t>
+          <t>2,17; 8,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,74</t>
+          <t>0,92; 6,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,97</t>
+          <t>3,43; 6,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>3,26; 5,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,98</t>
+          <t>2,0; 4,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,27</t>
+          <t>0,99; 2,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,03</t>
+          <t>2,66; 5,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,77</t>
+          <t>2,74; 5,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,05</t>
+          <t>1,96; 3,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,64</t>
+          <t>0,81; 2,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,05</t>
+          <t>3,39; 5,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,06</t>
+          <t>3,37; 5,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,65</t>
+          <t>2,1; 3,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,24</t>
+          <t>1,09; 2,25</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3972</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5501</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1152</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1941</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3972</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>3988</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2536; 9533</t>
+          <t>1377; 8127</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3919</t>
+          <t>617; 5190</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>529; 5137</t>
+          <t>553; 4931</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>422; 5177</t>
+          <t>471; 5703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1935; 8659</t>
+          <t>2601; 10453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>615; 5647</t>
+          <t>0; 4217</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>545; 4677</t>
+          <t>541; 5393</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>676; 6435</t>
+          <t>374; 5450</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5337; 14562</t>
+          <t>5622; 15516</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1119; 6945</t>
+          <t>1145; 7029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1426; 8041</t>
+          <t>1273; 7790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2047; 8749</t>
+          <t>1797; 8311</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5186</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3133</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2854</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3094</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2492; 9862</t>
+          <t>792; 7015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>618; 5294</t>
+          <t>750; 6686</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1214; 7007</t>
+          <t>1453; 8707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>756; 6444</t>
+          <t>0; 3089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>737; 6975</t>
+          <t>2490; 10137</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>746; 7032</t>
+          <t>623; 5387</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1561; 8466</t>
+          <t>1198; 6976</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>823; 6486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4544; 13783</t>
+          <t>4207; 13677</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2041; 9465</t>
+          <t>2045; 9808</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3673; 12649</t>
+          <t>3758; 12167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1109; 7212</t>
+          <t>1180; 7723</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5501</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4034</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2041</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>861</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5501</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4034</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>776</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1277</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2751</t>
+          <t>2633; 10064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>625; 6074</t>
+          <t>1452; 8678</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>530; 4773</t>
+          <t>1337; 8298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2883</t>
+          <t>0; 3097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2646; 10259</t>
+          <t>0; 3595</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1918; 8478</t>
+          <t>627; 5884</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1853; 9099</t>
+          <t>543; 4712</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2735; 11358</t>
+          <t>3216; 10788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2733; 10567</t>
+          <t>2716; 10479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2809; 10546</t>
+          <t>2600; 10112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>350; 4179</t>
+          <t>257; 3652</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10898</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4642</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7134</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>14545</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4299</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10898</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6173</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3798; 12221</t>
+          <t>5821; 16171</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9472; 22411</t>
+          <t>6639; 18196</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1699; 9410</t>
+          <t>1504; 9429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>435; 4595</t>
+          <t>1649; 11317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5832; 16037</t>
+          <t>3792; 12350</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6418; 17826</t>
+          <t>9483; 21174</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2028; 9524</t>
+          <t>1899; 9253</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1935; 11259</t>
+          <t>374; 4312</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11319; 24585</t>
+          <t>11713; 23994</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18194; 34280</t>
+          <t>18314; 34895</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4651; 15325</t>
+          <t>4618; 14731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2922; 14170</t>
+          <t>2678; 13187</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5772</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3134</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4806</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>5641</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6875</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5772</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>4734</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1137; 7107</t>
+          <t>2086; 9951</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2040; 9037</t>
+          <t>3433; 12802</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2601; 10287</t>
+          <t>2531; 11391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>661; 6412</t>
+          <t>818; 6384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1963; 10065</t>
+          <t>1184; 7052</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3463; 12744</t>
+          <t>2063; 9630</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2417; 11745</t>
+          <t>2982; 10224</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1012; 7431</t>
+          <t>631; 5923</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4211; 12990</t>
+          <t>4024; 13653</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6914; 18965</t>
+          <t>6932; 18286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6357; 17628</t>
+          <t>6511; 17820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2275; 9822</t>
+          <t>2270; 9484</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,44 +2899,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4076</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1976</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1378</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2483</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4076</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6053</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>893</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>607; 4883</t>
+          <t>1357; 8442</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4231</t>
+          <t>1953; 8684</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>603; 6011</t>
+          <t>0; 2637</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0; 5401</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5256</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4340</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1058; 6576</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1846; 8488</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2006; 9176</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3237</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3865</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3005; 10943</t>
+          <t>3057; 11388</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3136; 11333</t>
+          <t>2758; 10783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1145; 7396</t>
+          <t>1186; 7793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 4941</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>31195</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31290</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>23559</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>25900</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>19211</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>31195</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>31290</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16350; 31758</t>
+          <t>23460; 41940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19014; 35400</t>
+          <t>23274; 40699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13750; 26650</t>
+          <t>14225; 29683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5158; 14938</t>
+          <t>6810; 19145</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23618; 41305</t>
+          <t>17017; 32280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23315; 41158</t>
+          <t>18583; 34787</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14103; 28715</t>
+          <t>13135; 26391</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7569; 19776</t>
+          <t>5028; 14820</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44145; 66782</t>
+          <t>44878; 67505</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45405; 70448</t>
+          <t>46867; 70274</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30498; 50318</t>
+          <t>29027; 50087</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15450; 31503</t>
+          <t>14255; 29495</t>
         </is>
       </c>
     </row>
